--- a/hasil_clustering.xlsx
+++ b/hasil_clustering.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Hasil Cluster" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Centroid Iterasi" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Interpretasi" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Jarak Euclidean" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,36 +460,6 @@
           <t>komunikasi</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>cluster</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Jarak_C1</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Jarak_C2</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Jarak_C3</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Jarak_C4</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Jarak_C5</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -523,24 +494,6 @@
       <c r="H2" t="n">
         <v>5</v>
       </c>
-      <c r="I2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.492178761174748</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.27617663341483</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.8748897637790903</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.109126351029605</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.316611645107137</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -575,24 +528,6 @@
       <c r="H3" t="n">
         <v>5</v>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8338540040078959</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.175622516277429</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3.603838831161523</v>
-      </c>
-      <c r="M3" t="n">
-        <v>4.932882862316248</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.663583029720121</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -627,24 +562,6 @@
       <c r="H4" t="n">
         <v>5</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.667317390751957</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.825741858350554</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2.705732369307982</v>
-      </c>
-      <c r="M4" t="n">
-        <v>4.242640687119285</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.706555705501412</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -679,24 +596,6 @@
       <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.463800418053378</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.9660917830792958</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2.354402233379676</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.061194001072963</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -731,24 +630,6 @@
       <c r="H6" t="n">
         <v>5</v>
       </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.603219417297582</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.751190071541826</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.822357718539636</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.464101615137754</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.078845553259923</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -783,24 +664,6 @@
       <c r="H7" t="n">
         <v>5</v>
       </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.523257200869243</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2.756809750418044</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3.914203323068564</v>
-      </c>
-      <c r="M7" t="n">
-        <v>5.291502622129181</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.02846456692762</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -835,24 +698,6 @@
       <c r="H8" t="n">
         <v>5</v>
       </c>
-      <c r="I8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.419841005076113</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.336665001664586</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.523478800089121</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.3166247903554</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.474120190527959</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -887,24 +732,6 @@
       <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.052918685454953</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.914854215512676</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.357482566917239</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.696845502136473</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.473634158512925</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -939,24 +766,6 @@
       <c r="H10" t="n">
         <v>5</v>
       </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.9057110466368399</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.570562531918633</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2.643417167415626</v>
-      </c>
-      <c r="M10" t="n">
-        <v>4.041451884327381</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.692307692307692</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -991,24 +800,6 @@
       <c r="H11" t="n">
         <v>3</v>
       </c>
-      <c r="I11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2.611572801972022</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.160246899469287</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3.798960221617501</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.163331998932266</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.08240363688233</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1043,24 +834,6 @@
       <c r="H12" t="n">
         <v>4</v>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.093303480283494</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1.125462867742275</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2.726187588085621</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.60555127546399</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.926151388545986</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1095,24 +868,6 @@
       <c r="H13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.489038468967485</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.183215956619923</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2.078698548207745</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2.081665999466133</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.714884369969842</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1147,24 +902,6 @@
       <c r="H14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.108390974179125</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.8944271909999161</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2.826243853772645</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.943920288775949</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.842650088469486</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1199,24 +936,6 @@
       <c r="H15" t="n">
         <v>4</v>
       </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.202211503854459</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1.632993161855452</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3.619221661089407</v>
-      </c>
-      <c r="M15" t="n">
-        <v>4.39696865275764</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.865285485074175</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1251,24 +970,6 @@
       <c r="H16" t="n">
         <v>4</v>
       </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.349189571557681</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.341640786499874</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3.57287448684745</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4.203173404306164</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.844550585889507</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1303,24 +1004,6 @@
       <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.052918685454953</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.914854215512676</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4.357482566917239</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.696845502136473</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.473634158512925</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1355,24 +1038,6 @@
       <c r="H18" t="n">
         <v>5</v>
       </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.659005923272831</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.483293460696835</v>
-      </c>
-      <c r="L18" t="n">
-        <v>3.914203323068564</v>
-      </c>
-      <c r="M18" t="n">
-        <v>5.597618541248889</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.02846456692762</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1407,24 +1072,6 @@
       <c r="H19" t="n">
         <v>5</v>
       </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.034559084827928</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.96638416050035</v>
-      </c>
-      <c r="L19" t="n">
-        <v>3.557291243018249</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4.760952285695233</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.649103901188087</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1459,24 +1106,6 @@
       <c r="H20" t="n">
         <v>5</v>
       </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.603219417297582</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1.751190071541826</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.822357718539636</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.464101615137754</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.078845553259923</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1511,24 +1140,6 @@
       <c r="H21" t="n">
         <v>5</v>
       </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.523257200869243</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.756809750418044</v>
-      </c>
-      <c r="L21" t="n">
-        <v>3.914203323068564</v>
-      </c>
-      <c r="M21" t="n">
-        <v>5.291502622129181</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.02846456692762</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1563,24 +1174,6 @@
       <c r="H22" t="n">
         <v>4</v>
       </c>
-      <c r="I22" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4.381245542080471</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.9496835316263</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2.105255035721824</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.366501646120693</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.289797998030364</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1615,24 +1208,6 @@
       <c r="H23" t="n">
         <v>4</v>
       </c>
-      <c r="I23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.279322816101309</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.190890230020664</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.822357718539636</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.366501646120693</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.307692307692307</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1667,24 +1242,6 @@
       <c r="H24" t="n">
         <v>4</v>
       </c>
-      <c r="I24" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.073322713286062</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.175622516277429</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.852592444503674</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.23606797749979</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.466662873613461</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1719,24 +1276,6 @@
       <c r="H25" t="n">
         <v>4</v>
       </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.349189571557681</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1.341640786499874</v>
-      </c>
-      <c r="L25" t="n">
-        <v>3.57287448684745</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4.203173404306164</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.844550585889507</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1771,24 +1310,6 @@
       <c r="H26" t="n">
         <v>3</v>
       </c>
-      <c r="I26" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.412532383202348</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1.505545305418162</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2.157387537660844</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.449489742783178</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.737167660097879</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1823,24 +1344,6 @@
       <c r="H27" t="n">
         <v>5</v>
       </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1.603219417297582</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1.751190071541826</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.822357718539636</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.464101615137754</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.078845553259923</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1875,24 +1378,6 @@
       <c r="H28" t="n">
         <v>4</v>
       </c>
-      <c r="I28" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.253121103485214</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.6324555320336759</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2.664350846284844</v>
-      </c>
-      <c r="M28" t="n">
-        <v>3.366501646120693</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.906078722055979</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1927,24 +1412,6 @@
       <c r="H29" t="n">
         <v>5</v>
       </c>
-      <c r="I29" t="n">
-        <v>3</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.514023170139846</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.380476142847617</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.286204100310025</v>
-      </c>
-      <c r="M29" t="n">
-        <v>3.109126351029605</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.702709706633458</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1979,24 +1446,6 @@
       <c r="H30" t="n">
         <v>2</v>
       </c>
-      <c r="I30" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.99087152850135</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2.129162589689508</v>
-      </c>
-      <c r="L30" t="n">
-        <v>4.395564543300551</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.915780041490244</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.499506822278302</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2031,24 +1480,6 @@
       <c r="H31" t="n">
         <v>4</v>
       </c>
-      <c r="I31" t="n">
-        <v>5</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3.032377367677051</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.396076167186675</v>
-      </c>
-      <c r="L31" t="n">
-        <v>3.478327964999673</v>
-      </c>
-      <c r="M31" t="n">
-        <v>4.864839839775475</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.804265559008951</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2083,24 +1514,6 @@
       <c r="H32" t="n">
         <v>3</v>
       </c>
-      <c r="I32" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.078536143539486</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.5773502691896258</v>
-      </c>
-      <c r="L32" t="n">
-        <v>3.034777840832813</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2.886751345948129</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1.420475793278414</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2135,24 +1548,6 @@
       <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="I33" t="n">
-        <v>5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.251201700909988</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2.720294101747089</v>
-      </c>
-      <c r="L33" t="n">
-        <v>4.653420353638205</v>
-      </c>
-      <c r="M33" t="n">
-        <v>4.358898943540674</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.07977012839935</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2187,24 +1582,6 @@
       <c r="H34" t="n">
         <v>2</v>
       </c>
-      <c r="I34" t="n">
-        <v>5</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3.615288715994893</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2.408318915758459</v>
-      </c>
-      <c r="L34" t="n">
-        <v>3.034777840832814</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2.380476142847617</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.004432957045443</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2239,24 +1616,6 @@
       <c r="H35" t="n">
         <v>1</v>
       </c>
-      <c r="I35" t="n">
-        <v>4</v>
-      </c>
-      <c r="J35" t="n">
-        <v>5.202913847066853</v>
-      </c>
-      <c r="K35" t="n">
-        <v>3.741657386773941</v>
-      </c>
-      <c r="L35" t="n">
-        <v>3.798960221617502</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.154700538379251</v>
-      </c>
-      <c r="N35" t="n">
-        <v>4.180824074369598</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2291,24 +1650,6 @@
       <c r="H36" t="n">
         <v>5</v>
       </c>
-      <c r="I36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.728609994117884</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3.356585566713095</v>
-      </c>
-      <c r="L36" t="n">
-        <v>3.871389197818743</v>
-      </c>
-      <c r="M36" t="n">
-        <v>5.446711546122731</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3.01573781290964</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2343,24 +1684,6 @@
       <c r="H37" t="n">
         <v>5</v>
       </c>
-      <c r="I37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1.093303480283494</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2.081665999466133</v>
-      </c>
-      <c r="L37" t="n">
-        <v>3.381138678822875</v>
-      </c>
-      <c r="M37" t="n">
-        <v>4.795831523312719</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.389573010309087</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2395,24 +1718,6 @@
       <c r="H38" t="n">
         <v>4</v>
       </c>
-      <c r="I38" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.386485386504598</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1.460593486680443</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2.258044603655731</v>
-      </c>
-      <c r="M38" t="n">
-        <v>2.70801280154532</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.790516484187239</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2447,24 +1752,6 @@
       <c r="H39" t="n">
         <v>5</v>
       </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.667317390751957</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1.825741858350554</v>
-      </c>
-      <c r="L39" t="n">
-        <v>2.705732369307982</v>
-      </c>
-      <c r="M39" t="n">
-        <v>4.242640687119285</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.706555705501412</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2499,24 +1786,6 @@
       <c r="H40" t="n">
         <v>5</v>
       </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.8338540040078959</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2.175622516277429</v>
-      </c>
-      <c r="L40" t="n">
-        <v>3.603838831161523</v>
-      </c>
-      <c r="M40" t="n">
-        <v>4.932882862316248</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2.663583029720121</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2551,24 +1820,6 @@
       <c r="H41" t="n">
         <v>3</v>
       </c>
-      <c r="I41" t="n">
-        <v>4</v>
-      </c>
-      <c r="J41" t="n">
-        <v>4.250919018282988</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3.119829055146024</v>
-      </c>
-      <c r="L41" t="n">
-        <v>2.157387537660844</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1.414213562373095</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.914772507692145</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2603,24 +1854,6 @@
       <c r="H42" t="n">
         <v>3</v>
       </c>
-      <c r="I42" t="n">
-        <v>5</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2.840829544340878</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2.898275349237888</v>
-      </c>
-      <c r="L42" t="n">
-        <v>4.135065347984088</v>
-      </c>
-      <c r="M42" t="n">
-        <v>4.760952285695233</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1.823579937096877</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2655,24 +1888,6 @@
       <c r="H43" t="n">
         <v>3</v>
       </c>
-      <c r="I43" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.078536143539486</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.5773502691896258</v>
-      </c>
-      <c r="L43" t="n">
-        <v>3.034777840832813</v>
-      </c>
-      <c r="M43" t="n">
-        <v>2.886751345948129</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1.420475793278414</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2707,24 +1922,6 @@
       <c r="H44" t="n">
         <v>5</v>
       </c>
-      <c r="I44" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" t="n">
-        <v>3.419841005076113</v>
-      </c>
-      <c r="K44" t="n">
-        <v>3.336665001664586</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1.523478800089121</v>
-      </c>
-      <c r="M44" t="n">
-        <v>3.3166247903554</v>
-      </c>
-      <c r="N44" t="n">
-        <v>4.474120190527959</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2759,24 +1956,6 @@
       <c r="H45" t="n">
         <v>4</v>
       </c>
-      <c r="I45" t="n">
-        <v>5</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.017501548946122</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2.175622516277429</v>
-      </c>
-      <c r="L45" t="n">
-        <v>3.510126444206958</v>
-      </c>
-      <c r="M45" t="n">
-        <v>4.509249752822894</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1.669425724170054</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2811,24 +1990,6 @@
       <c r="H46" t="n">
         <v>4</v>
       </c>
-      <c r="I46" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1.716191277218248</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1.366260102127946</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1.940472132952553</v>
-      </c>
-      <c r="M46" t="n">
-        <v>2.943920288775949</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2.437381464269978</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2863,24 +2024,6 @@
       <c r="H47" t="n">
         <v>3</v>
       </c>
-      <c r="I47" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.137828922060884</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1.316561177208767</v>
-      </c>
-      <c r="L47" t="n">
-        <v>3.857012212824396</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.829708431025352</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1.336780553614059</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2915,24 +2058,6 @@
       <c r="H48" t="n">
         <v>4</v>
       </c>
-      <c r="I48" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1.302041665999979</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.9309493362512627</v>
-      </c>
-      <c r="L48" t="n">
-        <v>2.424158247696825</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3.415650255319866</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1.524940584738385</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2967,24 +2092,6 @@
       <c r="H49" t="n">
         <v>4</v>
       </c>
-      <c r="I49" t="n">
-        <v>3</v>
-      </c>
-      <c r="J49" t="n">
-        <v>3.833446556298914</v>
-      </c>
-      <c r="K49" t="n">
-        <v>3.464101615137754</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1.409841948938835</v>
-      </c>
-      <c r="M49" t="n">
-        <v>2.943920288775949</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3.973283560044602</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3019,24 +2126,6 @@
       <c r="H50" t="n">
         <v>4</v>
       </c>
-      <c r="I50" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.349189571557681</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1.341640786499874</v>
-      </c>
-      <c r="L50" t="n">
-        <v>3.57287448684745</v>
-      </c>
-      <c r="M50" t="n">
-        <v>4.203173404306164</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1.844550585889507</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3071,24 +2160,6 @@
       <c r="H51" t="n">
         <v>3</v>
       </c>
-      <c r="I51" t="n">
-        <v>5</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.166866977919964</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1.483239697419133</v>
-      </c>
-      <c r="L51" t="n">
-        <v>3.69517536629242</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.872983346207417</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.6923076923076925</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3123,24 +2194,6 @@
       <c r="H52" t="n">
         <v>3</v>
       </c>
-      <c r="I52" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.489038468967485</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1.183215956619923</v>
-      </c>
-      <c r="L52" t="n">
-        <v>2.078698548207745</v>
-      </c>
-      <c r="M52" t="n">
-        <v>2.081665999466133</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1.714884369969842</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3175,24 +2228,6 @@
       <c r="H53" t="n">
         <v>4</v>
       </c>
-      <c r="I53" t="n">
-        <v>5</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.017501548946122</v>
-      </c>
-      <c r="K53" t="n">
-        <v>2.175622516277429</v>
-      </c>
-      <c r="L53" t="n">
-        <v>3.510126444206958</v>
-      </c>
-      <c r="M53" t="n">
-        <v>4.509249752822894</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1.669425724170054</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3227,24 +2262,6 @@
       <c r="H54" t="n">
         <v>5</v>
       </c>
-      <c r="I54" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.195521008781287</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2.449489742783178</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1.696037502497083</v>
-      </c>
-      <c r="M54" t="n">
-        <v>3.829708431025352</v>
-      </c>
-      <c r="N54" t="n">
-        <v>2.977231150825173</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3279,24 +2296,6 @@
       <c r="H55" t="n">
         <v>1</v>
       </c>
-      <c r="I55" t="n">
-        <v>5</v>
-      </c>
-      <c r="J55" t="n">
-        <v>4.265596382687889</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2.70801280154532</v>
-      </c>
-      <c r="L55" t="n">
-        <v>4.593339246354309</v>
-      </c>
-      <c r="M55" t="n">
-        <v>2.943920288775949</v>
-      </c>
-      <c r="N55" t="n">
-        <v>2.590378190843498</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3331,24 +2330,6 @@
       <c r="H56" t="n">
         <v>3</v>
       </c>
-      <c r="I56" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.463800418053378</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0.9660917830792958</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2.354402233379676</v>
-      </c>
-      <c r="M56" t="n">
-        <v>2</v>
-      </c>
-      <c r="N56" t="n">
-        <v>2.061194001072963</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3382,24 +2363,6 @@
       </c>
       <c r="H57" t="n">
         <v>2</v>
-      </c>
-      <c r="I57" t="n">
-        <v>4</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.817107871150617</v>
-      </c>
-      <c r="K57" t="n">
-        <v>2.338090388900024</v>
-      </c>
-      <c r="L57" t="n">
-        <v>2.826243853772645</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.816496580927726</v>
-      </c>
-      <c r="N57" t="n">
-        <v>2.977231150825173</v>
       </c>
     </row>
   </sheetData>
@@ -3413,7 +2376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3447,26 +2410,6 @@
           <t>Komunikasi</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Kategori Transportasi</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Kategori Konsumsi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Kategori Hiburan</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Kategori Komunikasi</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -3478,36 +2421,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.73</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>4.33</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Sangat Boros</t>
-        </is>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3520,36 +2443,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="D3" t="n">
         <v>1.89</v>
       </c>
       <c r="E3" t="n">
-        <v>4.33</v>
+        <v>2.78</v>
       </c>
       <c r="F3" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
+        <v>3.22</v>
       </c>
     </row>
     <row r="4">
@@ -3562,36 +2465,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="D4" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="E4" t="n">
-        <v>2.35</v>
+        <v>4.06</v>
       </c>
       <c r="F4" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
+        <v>4.06</v>
       </c>
     </row>
     <row r="5">
@@ -3604,36 +2487,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.33</v>
+        <v>2.83</v>
       </c>
       <c r="D5" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="E5" t="n">
-        <v>1.33</v>
+        <v>4.83</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -3646,36 +2509,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.08</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.33</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sangat Boros</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3688,36 +2531,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>4.38</v>
+        <v>1.5</v>
       </c>
       <c r="F7" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Sangat Boros</t>
-        </is>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -3730,36 +2553,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.09</v>
+        <v>1.67</v>
       </c>
       <c r="D8" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>4.09</v>
+        <v>2.39</v>
       </c>
       <c r="F8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9">
@@ -3772,36 +2575,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="D9" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="E9" t="n">
-        <v>2.08</v>
+        <v>4.32</v>
       </c>
       <c r="F9" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
+        <v>3.96</v>
       </c>
     </row>
     <row r="10">
@@ -3814,36 +2597,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.33</v>
+        <v>2.88</v>
       </c>
       <c r="D10" t="n">
-        <v>1.67</v>
+        <v>3.12</v>
       </c>
       <c r="E10" t="n">
-        <v>1.33</v>
+        <v>4.88</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
+        <v>4.38</v>
       </c>
     </row>
     <row r="11">
@@ -3856,36 +2619,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.46</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>4.62</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Sangat Boros</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -3898,36 +2641,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.69</v>
+        <v>1.67</v>
       </c>
       <c r="E12" t="n">
-        <v>4.38</v>
+        <v>2.33</v>
       </c>
       <c r="F12" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Sangat Boros</t>
-        </is>
+        <v>1.33</v>
       </c>
     </row>
     <row r="13">
@@ -3940,36 +2663,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="D13" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="E13" t="n">
-        <v>3.92</v>
+        <v>2.33</v>
       </c>
       <c r="F13" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -3982,36 +2685,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1.16</v>
       </c>
       <c r="D14" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="E14" t="n">
-        <v>1.91</v>
+        <v>4.64</v>
       </c>
       <c r="F14" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
+        <v>3.84</v>
       </c>
     </row>
     <row r="15">
@@ -4024,36 +2707,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.33</v>
+        <v>3.43</v>
       </c>
       <c r="D15" t="n">
-        <v>1.67</v>
+        <v>2.71</v>
       </c>
       <c r="E15" t="n">
-        <v>1.33</v>
+        <v>4.86</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -4066,36 +2729,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2.46</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>4.62</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Sangat Boros</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -4108,36 +2751,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="D17" t="n">
-        <v>2.69</v>
+        <v>1.75</v>
       </c>
       <c r="E17" t="n">
-        <v>4.38</v>
+        <v>2.5</v>
       </c>
       <c r="F17" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Sangat Boros</t>
-        </is>
+        <v>1.5</v>
       </c>
     </row>
     <row r="18">
@@ -4150,36 +2773,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="D18" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="F18" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
+        <v>4.1</v>
       </c>
     </row>
     <row r="19">
@@ -4192,36 +2795,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.11</v>
+        <v>1.16</v>
       </c>
       <c r="D19" t="n">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="E19" t="n">
-        <v>1.67</v>
+        <v>4.64</v>
       </c>
       <c r="F19" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Sangat Boros</t>
-        </is>
+        <v>3.84</v>
       </c>
     </row>
     <row r="20">
@@ -4234,36 +2817,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.33</v>
+        <v>3.43</v>
       </c>
       <c r="D20" t="n">
-        <v>1.67</v>
+        <v>2.71</v>
       </c>
       <c r="E20" t="n">
-        <v>1.33</v>
+        <v>4.86</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -4276,36 +2839,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2.46</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>4.62</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Sangat Boros</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -4318,36 +2861,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.69</v>
+        <v>1.75</v>
       </c>
       <c r="E22" t="n">
-        <v>4.38</v>
+        <v>2.5</v>
       </c>
       <c r="F22" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Sangat Boros</t>
-        </is>
+        <v>1.5</v>
       </c>
     </row>
     <row r="23">
@@ -4360,36 +2883,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="D23" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="E23" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="F23" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
+        <v>4.1</v>
       </c>
     </row>
     <row r="24">
@@ -4402,36 +2905,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.11</v>
+        <v>1.16</v>
       </c>
       <c r="D24" t="n">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="E24" t="n">
-        <v>1.67</v>
+        <v>4.64</v>
       </c>
       <c r="F24" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Sangat Boros</t>
-        </is>
+        <v>3.84</v>
       </c>
     </row>
     <row r="25">
@@ -4444,36 +2927,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.33</v>
+        <v>3.43</v>
       </c>
       <c r="D25" t="n">
-        <v>1.67</v>
+        <v>2.71</v>
       </c>
       <c r="E25" t="n">
-        <v>1.33</v>
+        <v>4.86</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Sangat Irit</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -4486,36 +2949,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>2.46</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>4.62</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Irit</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Sangat Boros</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4567,22 +3010,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sangat Irit</t>
+          <t>Irit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Irit</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Sedang</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Boros</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sangat Boros</t>
+          <t>Irit</t>
         </is>
       </c>
     </row>
@@ -4594,7 +3037,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sangat Irit</t>
+          <t>Irit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4604,12 +3047,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Irit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Boros</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Sedang</t>
         </is>
       </c>
     </row>
@@ -4621,22 +3064,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Irit</t>
+          <t>Sangat Irit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irit</t>
+          <t>Sedang</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Irit</t>
+          <t>Sangat Boros</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sangat Boros</t>
+          <t>Boros</t>
         </is>
       </c>
     </row>
@@ -4648,22 +3091,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sangat Irit</t>
+          <t>Sedang</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irit</t>
+          <t>Sedang</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sangat Irit</t>
+          <t>Sangat Boros</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Irit</t>
+          <t>Boros</t>
         </is>
       </c>
     </row>
@@ -4675,12 +3118,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Irit</t>
+          <t>Sangat Boros</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irit</t>
+          <t>Sangat Boros</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4690,8 +3133,1459 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sedang</t>
-        </is>
+          <t>Sangat Boros</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>nama</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Jarak_C1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Jarak_C2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Jarak_C3</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Jarak_C4</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Jarak_C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Novan Arrijal Ghifari Hakim </t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.848701079585163</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.616322987524461</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.946035985644328</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.292851200376205</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.830951894845301</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dzakwan</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.506939094329987</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.051638903933426</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.315750736271882</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.64575131106459</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.47213595499958</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Muhammad Fuad Hadziq </t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4.038873605350878</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.216416025930151</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.418167832098867</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.777460299317654</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4.58257569495584</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Moh. Rafli Dwi Saputra</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.677050983124842</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.487447478064351</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.921249593363652</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.295017884191656</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.744562646538029</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Muhammad Daffa Safaraz</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.579455265819088</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.346291201783626</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.08115352629257</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.295017884191656</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.385164807134504</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Zora Riyadhul Jinan</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4.879805323985784</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.465905365124674</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.921249593363653</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.927700218845599</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.123105625617661</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Muhammad Dzaka</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.038873605350878</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.926784886799769</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.853725470243047</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.675162334843877</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Salwa</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.610076627227638</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.49463875100131</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.952229494705989</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.229329872987804</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5.830951894845301</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haddi Fauzan Nurrosid </t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.848701079585163</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.052437575177379</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.432201103197452</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.853569193634026</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.099019513592784</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>nazhwa sava azahra</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.288236609491476</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.195700236254959</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.119245148631937</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.309307341415954</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.123105625617661</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Khozinul Ilmi</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.211308144666282</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.027929979067325</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8313843876330609</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.591193878173865</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.69041575982343</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rifal Hafidz Jaelani </t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.677050983124842</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.346291201783626</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.090741495259516</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.64575131106459</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.099019513592784</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Muhamad zaldi nugraha</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2.193741096848031</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.052437575177379</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.446098198602017</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.070196678027062</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.795831523312719</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ratuw</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.783186487605389</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.917618892179032</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6412487816752561</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.449489742783178</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.58257569495584</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Adi Tri Saputra</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.579455265819088</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.795084971874737</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6717142249498668</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.535462764185549</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.099019513592784</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">windi rihanafsa </t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.610076627227638</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.49463875100131</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.952229494705989</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.229329872987804</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.830951894845301</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Daffa fauzan</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5.129571132170798</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.756660751252367</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.125891872730085</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.195228609334394</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.23606797749979</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PZA</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.337337893224368</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.934706118165838</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.33086438076913</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.725540575476987</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Afif Fadilah Rahman</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.579455265819088</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.346291201783626</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.08115352629257</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.295017884191656</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.385164807134504</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elbima Dwiputra Hardy </t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4.879805323985784</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.465905365124674</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.921249593363653</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.927700218845599</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.123105625617661</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ALL HARTAWAN</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.848701079585163</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.648112535373072</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4.648784787447146</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.964124835860459</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5.196152422706632</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Raffi Akbar Ardiansyah </t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.211308144666282</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.706604816587601</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.516187592370648</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.927248223318863</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.605551275463989</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Daffa Akhdan Andetri</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2.704163456597992</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.382931668593933</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.054701294725885</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.123105625617661</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6.48074069840786</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Reivani</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.579455265819088</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.795084971874737</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6717142249498668</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.535462764185549</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.099019513592784</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ariq</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2.076655965729519</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.585086748414736</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.08115352629257</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.563479777846623</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.58257569495584</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Daffa Muttaqin</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.579455265819088</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.346291201783626</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.08115352629257</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.295017884191656</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.385164807134504</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Kgs M Zahid Al Fatih</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2.968585521759479</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.847295320191117</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8551023330572778</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.672612419124244</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5.196152422706632</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Aryadi Rahman Razan</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.579455265819088</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.188486432400472</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.934484622552996</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.946064947695181</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.830951894845301</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Alvina</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2.883140648667699</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3.59339672176619</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.941957775030137</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5.385164807134504</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>bahlil ganteng</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4.451123453691214</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3.407711842277747</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.269740050829729</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.647508942095828</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>M Zidni A</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.193741096848031</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.147673159491453</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.1879393923934</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.853569193634026</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5.477225575051661</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Amanda Debby</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3.43693177121688</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.951265620026069</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.3939924811912</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.401680257083045</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5.099019513592784</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Aufaa Prie Adrianto</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.677050983124842</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.571478174124758</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.119487137335238</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.853569193634026</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5.099019513592784</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Akmal Mahesa Ruhyana</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.677050983124842</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3.43693177121688</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4.648784787447145</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.503245795502349</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7.54983443527075</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Tuska Pratama</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4.981214711292819</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3.662308015445997</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3.132283512072303</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.362770287738494</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.16227766016838</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Revandika putra </t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4.337337893224368</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.865745976181421</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.565630863262474</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.889822365046136</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4.242640687119285</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balhan Armenia </t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2.704163456597992</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.520690632574555</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.247487486060823</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.505098327538656</v>
+      </c>
+      <c r="G38" t="n">
+        <v>6.082762530298219</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nisa Nur Azizah </t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4.038873605350878</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.216416025930151</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.418167832098867</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.777460299317654</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4.58257569495584</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.506939094329987</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3.051638903933426</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.315750736271882</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.64575131106459</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4.47213595499958</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Oki</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.304886114323222</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.076655965729518</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4.119611632180878</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.566962103755937</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.708203932499369</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Raffi</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.976493430146717</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3.689512162874653</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.532034754895754</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.690308509457033</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Given Al Yusuf</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.193741096848031</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.147673159491453</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.1879393923934</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.853569193634026</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5.477225575051661</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dede Syaifatullah Rasyidin </t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4.038873605350878</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.926784886799769</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.853725470243047</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4.675162334843877</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Prawira Rizki Maulana</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3.848701079585163</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3.002082610455615</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.952229494705989</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.8451542547285167</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3.741657386773941</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Mohamad Thareq Hanne</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2.883140648667699</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.30862523283024</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.723716914113219</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.070597894314953</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Zahid abdul majid</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2.968585521759479</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3.002082610455615</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.063578864024666</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.725540575476987</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5.385164807134504</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Virdianti Adinda</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2.968585521759479</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.735655495770978</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.1879393923934</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.812653934349931</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4.47213595499958</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zuyyi </t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3.50891721190455</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.027929979067325</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.10989050949049</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3.891382420536067</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sabili Mardhotillah Romdhani</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3.579455265819088</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.795084971874737</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.6717142249498668</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.535462764185549</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5.099019513592784</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Isna</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2.968585521759479</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.934706118165838</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.345808307300858</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.889822365046136</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4.69041575982343</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Sgt</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1.677050983124842</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.346291201783626</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.090741495259516</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.64575131106459</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5.099019513592784</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Evergereen</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3.848701079585163</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3.002082610455615</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.952229494705989</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.8451542547285167</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3.741657386773941</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zahra'Ateltline Mufidah </t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3.848701079585163</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.735655495770978</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.773301281866072</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.267786838055363</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4.123105625617661</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>indah a winatha</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1.82002747232013</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3.783186487605389</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3.288038929209932</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4.309458036856673</v>
+      </c>
+      <c r="G55" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Vania Hissana Khaerunnisa</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1.677050983124842</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.487447478064351</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.921249593363652</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.295017884191656</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5.744562646538029</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Abiyu Zafran</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.9013878188659973</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2.238861317723811</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3.26361762466132</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4.309458036856673</v>
+      </c>
+      <c r="G57" t="n">
+        <v>6.557438524302</v>
       </c>
     </row>
   </sheetData>
